--- a/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
+++ b/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
@@ -107,7 +107,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,9 +130,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -504,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="11" min="1" max="1"/>
@@ -661,7 +658,7 @@
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>HTTP POST /v1/mom-prompt AND the Kafka consumer (mom-prompt.jobs → mom-prompt.acks) in ONE pod. Dockerfile at the repo root (build context: .). replicas 1, strategy Recreate, terminationGracePeriodSeconds 3600. Route only for the HTTP endpoint; its timeout must be 3600s (haproxy.router.openshift.io/timeout). Liveness: GET / on 8000. BEFORE DEPLOY: create Kafka topics mom-prompt.jobs and mom-prompt.acks (1 partition, replication 1).</t>
+          <t>ONE service, ONE pod: the HTTP API (POST /v1/mom-prompt), the Kafka consumer (mom-prompt.jobs → mom-prompt.acks) and the minutes writer (Llama 3.3 70B on IBM watsonx) all run in this container — no separate llama pod. Dockerfile at the repo root (build context: .). replicas 1, strategy Recreate, terminationGracePeriodSeconds 3600. Route only for the HTTP endpoint; its timeout must be 3600s. Liveness and readiness: GET / on 8000. BEFORE DEPLOY: create Kafka topics mom-prompt.jobs and mom-prompt.acks (1 partition, replication 1).</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -671,56 +668,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>mom-prompt-llama</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>https://github.com/Shxbhxm07/momPromptService.git</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>8001</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>250m request, no limit</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>256Mi request, 1Gi limit</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>Internal minutes writer for THIS service only — not the shared llama-service. Dockerfile: llama/ (build context: llama/). Calls IBM watsonx (Cloud Pak for Data), Llama 3.3 70B. No GPU. Liveness and readiness: GET / on 8001.</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -841,12 +798,12 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>LLAMA_URL</t>
+          <t>JOB_KIND</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>http://mom-prompt-llama:8001</t>
+          <t>prompt</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -861,7 +818,7 @@
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>This service's own writer (row above), not llama-service</t>
+          <t>Any other value refuses to start</t>
         </is>
       </c>
     </row>
@@ -871,19 +828,19 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>JOB_KIND</t>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>ENABLE_KAFKA</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>prompt</t>
+          <t>true</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -893,7 +850,7 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Any other value refuses to start</t>
+          <t>false leaves only the HTTP endpoint</t>
         </is>
       </c>
     </row>
@@ -903,19 +860,19 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>ENABLE_KAFKA</t>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>KAFKA_BOOTSTRAP</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>kafka-service.teamsync.svc.cluster.local:9092</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -925,7 +882,7 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>false leaves only the HTTP endpoint</t>
+          <t>Broker host:port</t>
         </is>
       </c>
     </row>
@@ -935,14 +892,14 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>KAFKA_BOOTSTRAP</t>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>KAFKA_JOB_TOPIC</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>kafka-service.teamsync.svc.cluster.local:9092</t>
+          <t>mom-prompt.jobs</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -957,7 +914,7 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Broker host:port</t>
+          <t>Topic the jobs arrive on — create before deploy</t>
         </is>
       </c>
     </row>
@@ -967,14 +924,14 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>KAFKA_JOB_TOPIC</t>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>KAFKA_ACK_TOPIC</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt.jobs</t>
+          <t>mom-prompt.acks</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -989,7 +946,7 @@
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>Topic the jobs arrive on — create before deploy</t>
+          <t>Topic the acks are sent to — create before deploy</t>
         </is>
       </c>
     </row>
@@ -999,14 +956,14 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>KAFKA_ACK_TOPIC</t>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>KAFKA_GROUP_ID</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt.acks</t>
+          <t>mom-prompt-consumer</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
@@ -1021,7 +978,7 @@
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Topic the acks are sent to — create before deploy</t>
+          <t>Must differ from mom-consumer's group</t>
         </is>
       </c>
     </row>
@@ -1033,12 +990,12 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>KAFKA_GROUP_ID</t>
+          <t>MINIO_ENDPOINT</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-consumer</t>
+          <t>minio-service.teamsync.svc.cluster.local:9000</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
@@ -1053,7 +1010,7 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>Must differ from mom-consumer's group</t>
+          <t>host:port, no scheme</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1022,12 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>MINIO_ENDPOINT</t>
+          <t>MINIO_ACCESS_KEY</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>minio-service.teamsync.svc.cluster.local:9000</t>
+          <t>[provided separately — not in this sheet]</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
@@ -1080,14 +1037,10 @@
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>host:port, no scheme</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -1095,9 +1048,9 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>MINIO_ACCESS_KEY</t>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>MINIO_SECRET_KEY</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -1123,27 +1076,31 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>MINIO_SECRET_KEY</t>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>MINIO_SECURE</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>[provided separately — not in this sheet]</t>
+          <t>false</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>true if MinIO uses TLS</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -1153,17 +1110,17 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>MINIO_SECURE</t>
+          <t>MINIO_SUMMARY_BUCKET</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>mom</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1173,7 +1130,7 @@
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>true if MinIO uses TLS</t>
+          <t>Bucket for the generated .docx — must already exist</t>
         </is>
       </c>
     </row>
@@ -1183,14 +1140,14 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>MINIO_SUMMARY_BUCKET</t>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>ELASTIC_URL</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>mom</t>
+          <t>http://elasticsearch-service.teamsync.svc.cluster.local:9200</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -1203,11 +1160,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>Bucket for the generated .docx — must already exist</t>
-        </is>
-      </c>
+      <c r="F31" s="13" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -1215,14 +1168,14 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>ELASTIC_URL</t>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>ELASTIC_USER</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>http://elasticsearch-service.teamsync.svc.cluster.local:9200</t>
+          <t>[provided separately — not in this sheet]</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -1232,10 +1185,14 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Read from the Secret</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
@@ -1245,7 +1202,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>ELASTIC_USER</t>
+          <t>ELASTIC_PASSWORD</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -1263,11 +1220,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>Read from the Secret</t>
-        </is>
-      </c>
+      <c r="F33" s="13" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
@@ -1277,12 +1230,12 @@
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>ELASTIC_PASSWORD</t>
+          <t>ELASTIC_INDEX_ATTACHED</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>[provided separately — not in this sheet]</t>
+          <t>mom-attached</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -1292,10 +1245,14 @@
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>Index for the minutes; the service creates it if missing</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
@@ -1303,19 +1260,19 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>ELASTIC_INDEX_ATTACHED</t>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>ENABLE_CHUNK_INDEX</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>mom-attached</t>
+          <t>true</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -1325,7 +1282,7 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>Index for the minutes; the service creates it if missing</t>
+          <t>Also write search chunks to CHUNK_INDEX</t>
         </is>
       </c>
     </row>
@@ -1335,14 +1292,14 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>ENABLE_CHUNK_INDEX</t>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>CHUNK_INDEX</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>mom_v1</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
@@ -1357,7 +1314,7 @@
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>Also write search chunks to CHUNK_INDEX</t>
+          <t>Doc-ingest index — must already exist; never created by this service</t>
         </is>
       </c>
     </row>
@@ -1367,19 +1324,19 @@
           <t>mom-prompt-service</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>CHUNK_INDEX</t>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>VLLM_API_BASE</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>mom_v1</t>
+          <t>https://cpd-watsonx-imir.apps.ocp4.iaf.in/ml/v1/text/chat?version=2023-05-29</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -1389,24 +1346,24 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Doc-ingest index — must already exist; never created by this service</t>
+          <t>Minutes writer (in this pod). Full URL including ?version= — same as the offline-mom cluster overlays</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>mom-prompt-service</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>VLLM_API_BASE</t>
+          <t>LLM_MODEL_PATH</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>https://cpd-watsonx-imir.apps.ocp4.iaf.in/ml/v1/text/chat?version=2023-05-29</t>
+          <t>meta-llama/llama-3-3-70b-instruct</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -1421,24 +1378,24 @@
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>Full URL including ?version= — same as the offline-mom cluster overlays</t>
+          <t>Llama 3.3 70B</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>LLM_MODEL_PATH</t>
+          <t>mom-prompt-service</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>WATSONX_PROJECT_ID</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>meta-llama/llama-3-3-70b-instruct</t>
+          <t>[to be provided]</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
@@ -1453,24 +1410,24 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>Llama 3.3 70B</t>
+          <t>watsonx project for MoM</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>WATSONX_PROJECT_ID</t>
+          <t>mom-prompt-service</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>LLM_AUTH_MODE</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>[to be provided]</t>
+          <t>cp4d</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -1485,24 +1442,24 @@
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>watsonx project for MoM</t>
+          <t>Cloud Pak for Data: token from username + API key</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>mom-prompt-service</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>LLM_AUTH_MODE</t>
+          <t>CP4D_AUTH_URL</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>cp4d</t>
+          <t>https://cpd-watsonx-imir.apps.ocp4.iaf.in/icp4d-api/v1/authorize</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -1517,24 +1474,24 @@
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>Cloud Pak for Data: token from username + API key</t>
+          <t>Token endpoint</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>mom-prompt-service</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>CP4D_AUTH_URL</t>
+          <t>CP4D_USERNAME</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>https://cpd-watsonx-imir.apps.ocp4.iaf.in/icp4d-api/v1/authorize</t>
+          <t>[provided separately — not in this sheet]</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -1544,24 +1501,20 @@
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>Token endpoint</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>mom-prompt-service</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>CP4D_USERNAME</t>
+          <t>CP4D_API_KEY</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
@@ -1584,17 +1537,17 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>mom-prompt-service</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>CP4D_API_KEY</t>
+          <t>LLM_VERIFY_SSL</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>[provided separately — not in this sheet]</t>
+          <t>false</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -1604,30 +1557,34 @@
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F44" s="13" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>Cluster certificate is self-signed</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>mom-prompt-service</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>LLM_VERIFY_SSL</t>
+          <t>LLM_PROVIDER_ORDER</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>(empty)</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1637,29 +1594,29 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>Cluster certificate is self-signed</t>
+          <t>OpenRouter-only setting — must stay empty on watsonx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>mom-prompt-service</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>LLM_PROVIDER_ORDER</t>
+          <t>LLM_IS_REASONING</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>(empty)</t>
+          <t>false</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -1669,29 +1626,29 @@
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>OpenRouter-only setting — must stay empty on watsonx</t>
+          <t>Llama is not a reasoning model; the output budgets key on this</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>mom-prompt-service</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>LLM_IS_REASONING</t>
+          <t>MODEL_CONTEXT_LIMIT</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -1701,24 +1658,24 @@
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>Llama is not a reasoning model; the output budgets key on this</t>
+          <t>Tested value in the cluster overlays</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>mom-prompt-service</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>MODEL_CONTEXT_LIMIT</t>
+          <t>LLM_CONCURRENCY</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
@@ -1733,24 +1690,24 @@
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>Tested value in the cluster overlays</t>
+          <t>Parallel LLM calls per job</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>mom-prompt-service</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>LLM_CONCURRENCY</t>
+          <t>MOM_WINDOW_KEY_POINTS</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>true</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
@@ -1765,24 +1722,24 @@
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>Parallel LLM calls per job</t>
+          <t>Re-reads long input in pieces so key points are not missed</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-llama</t>
+          <t>all</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>MOM_WINDOW_KEY_POINTS</t>
+          <t>(other settings)</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>Defaults in app/config.py and llama/config.py</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
@@ -1796,38 +1753,6 @@
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
-        <is>
-          <t>Re-reads long input in pieces so key points are not missed</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>(other settings)</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>Defaults in app/config.py and llama/config.py</t>
-        </is>
-      </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>Leave as shipped</t>
         </is>

--- a/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
+++ b/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="11" min="1" max="1"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>https://cpd-watsonx-imir.apps.ocp4.iaf.in/ml/v1/text/chat?version=2023-05-29</t>
+          <t>https://us-south.ml.cloud.ibm.com/ml/v1/text/chat?version=2023-05-29</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Minutes writer (in this pod). Full URL including ?version= — same as the offline-mom cluster overlays</t>
+          <t>Minutes writer (in this pod). IBM Cloud us-south. NOT Cloud Pak: cpd-watsonx-imir.apps.ocp4.iaf.in does not resolve from this cluster</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>[to be provided]</t>
+          <t>7ade6186-5397-4ed2-99f7-dce2cc6eda66</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>cp4d</t>
+          <t>iam</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>Cloud Pak for Data: token from username + API key</t>
+          <t>IBM Cloud API key -&gt; IAM token. Set ONCE: a second, empty entry overrides it</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>CP4D_AUTH_URL</t>
+          <t>WATSONX_API_KEY</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>https://cpd-watsonx-imir.apps.ocp4.iaf.in/icp4d-api/v1/authorize</t>
+          <t>[provided separately — not in this sheet]</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>Token endpoint</t>
+          <t>IBM Cloud API key — paste as text, never retype from a screenshot</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>CP4D_USERNAME</t>
+          <t>LLM_VERIFY_SSL</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>[provided separately — not in this sheet]</t>
+          <t>true</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -1501,10 +1501,14 @@
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>IBM Cloud has a valid public certificate</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
@@ -1514,25 +1518,29 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>CP4D_API_KEY</t>
+          <t>LLM_PROVIDER_ORDER</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>[provided separately — not in this sheet]</t>
+          <t>(empty)</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>OpenRouter-only setting — must stay empty on watsonx</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
@@ -1542,7 +1550,7 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>LLM_VERIFY_SSL</t>
+          <t>LLM_IS_REASONING</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
@@ -1562,7 +1570,7 @@
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>Cluster certificate is self-signed</t>
+          <t>Llama is not a reasoning model; the output budgets key on this</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1582,12 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>LLM_PROVIDER_ORDER</t>
+          <t>MODEL_CONTEXT_LIMIT</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>(empty)</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
@@ -1594,7 +1602,7 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>OpenRouter-only setting — must stay empty on watsonx</t>
+          <t>Tested value in the cluster overlays</t>
         </is>
       </c>
     </row>
@@ -1606,17 +1614,17 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>LLM_IS_REASONING</t>
+          <t>LLM_CONCURRENCY</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -1626,7 +1634,7 @@
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>Llama is not a reasoning model; the output budgets key on this</t>
+          <t>Parallel LLM calls per job</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1646,12 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>MODEL_CONTEXT_LIMIT</t>
+          <t>MOM_WINDOW_KEY_POINTS</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>true</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
@@ -1658,24 +1666,24 @@
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>Tested value in the cluster overlays</t>
+          <t>Re-reads long input in pieces so key points are not missed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>mom-prompt-service</t>
+          <t>all</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>LLM_CONCURRENCY</t>
+          <t>(other settings)</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Defaults in app/config.py and llama/config.py</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
@@ -1689,70 +1697,6 @@
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
-        <is>
-          <t>Parallel LLM calls per job</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>mom-prompt-service</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>MOM_WINDOW_KEY_POINTS</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="inlineStr">
-        <is>
-          <t>Re-reads long input in pieces so key points are not missed</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>(other settings)</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="inlineStr">
-        <is>
-          <t>Defaults in app/config.py and llama/config.py</t>
-        </is>
-      </c>
-      <c r="D50" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>Leave as shipped</t>
         </is>

--- a/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
+++ b/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>[provided separately — not in this sheet]</t>
+          <t>[plain env value in the Deployment — provided separately, not in this sheet]</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>[provided separately — not in this sheet]</t>
+          <t>[plain env value in the Deployment — provided separately, not in this sheet]</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr"/>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>[provided separately — not in this sheet]</t>
+          <t>[plain env value in the Deployment — provided separately, not in this sheet]</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>[provided separately — not in this sheet]</t>
+          <t>[plain env value in the Deployment — provided separately, not in this sheet]</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>[provided separately — not in this sheet]</t>
+          <t>[plain env value in the Deployment — provided separately, not in this sheet]</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">

--- a/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
+++ b/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="11" min="1" max="1"/>
@@ -524,6 +524,7 @@
       </c>
     </row>
     <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -556,6 +557,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
@@ -751,6 +753,8 @@
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="2" t="n"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
@@ -1587,7 +1591,7 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>65536</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
@@ -1602,7 +1606,7 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>Tested value in the cluster overlays</t>
+          <t>Main read takes the whole transcript in one call up to this (3-hour meeting: 1 call, not 10 + merge). CP4D: confirm its limit first</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1642,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" s="11">
       <c r="A47" s="13" t="inlineStr">
         <is>
           <t>mom-prompt-service</t>
@@ -1670,33 +1674,225 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" s="11">
       <c r="A48" s="13" t="inlineStr">
         <is>
+          <t>mom-prompt-service</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>MOM_WINDOW_CHARS</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>Chunk size: characters per window call. Decides most model calls (6000: 12 for a 45-min meeting; 1800: 27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" s="11">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>mom-prompt-service</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>ENABLE_OCR</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>OCR (Tesseract, in this pod) for scanned PDF pages only. false skips them</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" s="11">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>mom-prompt-service</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>OCR_LANGS</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>eng+hin</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>English FIRST (hin+eng loses the digit 1). Installed: eng, hin. /health shows it</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" s="11">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>mom-prompt-service</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>OCR_DPI</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>Scan resolution; below 300 Hindi vowel signs drop out</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" s="11">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>mom-prompt-service</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>OCR_MAX_PAGES</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>Most scanned pages read per document, about 1 s each</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>mom-prompt-service</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>MIN_PAGE_TEXT_CHARS</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>A PDF page with less text of its own than this is OCR'd</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>(other settings)</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>Defaults in app/config.py and llama/config.py</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
         <is>
           <t>Leave as shipped</t>
         </is>

--- a/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
+++ b/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="11" min="1" max="1"/>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>Chunk size: characters per window call. Decides most model calls (6000: 12 for a 45-min meeting; 1800: 27)</t>
+          <t>Chunk size: characters per window call (1800: 25 calls for a 45-min meeting; 6000: 12). 1800 until a full test shows 6000 loses nothing</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>ENABLE_OCR</t>
+          <t>ESSENCE_POINTS_PER_ITEM</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>OCR (Tesseract, in this pod) for scanned PDF pages only. false skips them</t>
+          <t>0 = shortening OFF: every verified point printed (accuracy first). A number &gt;0 deletes real points</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>OCR_LANGS</t>
+          <t>ENABLE_OCR</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>eng+hin</t>
+          <t>true</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>English FIRST (hin+eng loses the digit 1). Installed: eng, hin. /health shows it</t>
+          <t>OCR (Tesseract, in this pod) for scanned PDF pages only. false skips them</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>OCR_DPI</t>
+          <t>OCR_LANGS</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>eng+hin</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>Scan resolution; below 300 Hindi vowel signs drop out</t>
+          <t>English FIRST (hin+eng loses the digit 1). Installed: eng, hin. /health shows it</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>OCR_MAX_PAGES</t>
+          <t>OCR_DPI</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>Most scanned pages read per document, about 1 s each</t>
+          <t>Scan resolution; below 300 Hindi vowel signs drop out</t>
         </is>
       </c>
     </row>
@@ -1842,12 +1842,12 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>MIN_PAGE_TEXT_CHARS</t>
+          <t>OCR_MAX_PAGES</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
@@ -1862,37 +1862,69 @@
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>A PDF page with less text of its own than this is OCR'd</t>
+          <t>Most scanned pages read per document, about 1 s each</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
+          <t>mom-prompt-service</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>MIN_PAGE_TEXT_CHARS</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>A PDF page with less text of its own than this is OCR'd</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>(other settings)</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
         <is>
           <t>Defaults in app/config.py and llama/config.py</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
         <is>
           <t>Leave as shipped</t>
         </is>

--- a/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
+++ b/deploy/Service_Onboarding_Form_mom-prompt-service.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="11" min="1" max="1"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>Parallel LLM calls per job</t>
+          <t>Model calls in flight at once for the pod; IBM allows 8 requests a second</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>Most scanned pages read per document, about 1 s each</t>
+          <t>Most scanned pages read per document; 0 = every page (a number skips the pages after it)</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>MIN_PAGE_TEXT_CHARS</t>
+          <t>OCR_WORKERS</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
@@ -1894,37 +1894,69 @@
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>A PDF page with less text of its own than this is OCR'd</t>
+          <t>Scanned pages read at the same time, one CPU core each (requests.cpu 2)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
+          <t>mom-prompt-service</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>MIN_PAGE_TEXT_CHARS</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>A PDF page with less text of its own than this is OCR'd</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
           <t>all</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>(other settings)</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C56" s="13" t="inlineStr">
         <is>
           <t>Defaults in app/config.py and llama/config.py</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F55" s="13" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>Leave as shipped</t>
         </is>
